--- a/esyluban/examples/release/DataTables/test/external_type.xlsx
+++ b/esyluban/examples/release/DataTables/test/external_type.xlsx
@@ -606,9 +606,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="H3:J3"/>
     <mergeCell ref="E2:G2"/>
-    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="E3:G3"/>
     <mergeCell ref="H2:J2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
